--- a/backend/complaints_export.xlsx
+++ b/backend/complaints_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,17 +491,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RK-20260327093506268929</t>
+          <t>RK-20260328091242781383</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>USR-20260327093404026628</t>
+          <t>USR-20260328091108754735</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mani</t>
+          <t>Sakthi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Account blocked</t>
+          <t>Account Blocked Click Me - http://bit.ly/click-me</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>uploads\RK-20260327093506268929_Screenshot 2026-03-25 141040.png</t>
+          <t>uploads\RK-20260328091242781383_Screenshot 2025-11-29 200927.png</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Detected keyword: blocked; Detected keyword: account; URL submitted for analysis; Shortened URL detected; Non-secure HTTP link detected</t>
+          <t>Detected keyword: click; Detected keyword: blocked; Detected keyword: account; URL submitted for analysis; Shortened URL detected; Non-secure HTTP link detected</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -554,29 +554,29 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-03-27 09:35:06</t>
+          <t>2026-03-28 09:12:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RK-20260326225828831979</t>
+          <t>RK-20260327093506268929</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>USR-20260326214559598116</t>
+          <t>USR-20260327093404026628</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>siva</t>
+          <t>Mani</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Family Member</t>
+          <t>Serving Personnel</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>http://bit.ly/xyz</t>
+          <t>http://bit.ly/click-me</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>uploads\RK-20260326225828831979_Screenshot 2026-03-26 201849.png</t>
+          <t>uploads\RK-20260327093506268929_Screenshot 2026-03-25 141040.png</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -619,19 +619,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-03-26 22:58:28</t>
+          <t>2026-03-27 09:35:06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RK-20260326214640403757</t>
+          <t>RK-20260326225828831979</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,41 +646,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Serving Personnel</t>
+          <t>Family Member</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Click Me</t>
+          <t>Account blocked</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>http://bit.ly/click-me</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>http://bit.ly/xyz</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>uploads\RK-20260326225828831979_Screenshot 2026-03-26 201849.png</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Suspicious Communication</t>
+          <t>High-Risk Social Engineering</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Detected keyword: click; URL submitted for analysis; Shortened URL detected; Non-secure HTTP link detected</t>
+          <t>Detected keyword: blocked; Detected keyword: account; URL submitted for analysis; Shortened URL detected; Non-secure HTTP link detected</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Proceed cautiously. Verify the message and sender before taking action.</t>
+          <t>Avoid clicking links or sharing credentials. Verify through official channels immediately.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -690,24 +694,24 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-03-26 21:46:40</t>
+          <t>2026-03-26 22:58:28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RK-20260326212013847331</t>
+          <t>RK-20260326214640403757</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>USR-20260326210152993767</t>
+          <t>USR-20260326214559598116</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boomesh</t>
+          <t>siva</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -717,40 +721,106 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Account blocked</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>Click Me</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>http://bit.ly/click-me</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
+          <t>Suspicious Communication</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>55</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Detected keyword: click; URL submitted for analysis; Shortened URL detected; Non-secure HTTP link detected</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Proceed cautiously. Verify the message and sender before taking action.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:46:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RK-20260326212013847331</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>USR-20260326210152993767</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Boomesh</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Serving Personnel</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Account blocked</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>Low-Risk Report</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" t="n">
         <v>10</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Detected keyword: account</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Monitor the case and verify authenticity before proceeding.</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>2026-03-26 21:20:13</t>
         </is>
